--- a/branches/examples/ValueSet-condition-valueset.xlsx
+++ b/branches/examples/ValueSet-condition-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T16:43:38+00:00</t>
+    <t>2025-01-30T12:44:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/examples/ValueSet-condition-valueset.xlsx
+++ b/branches/examples/ValueSet-condition-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-30T12:44:56+00:00</t>
+    <t>2025-01-30T13:04:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/examples/ValueSet-condition-valueset.xlsx
+++ b/branches/examples/ValueSet-condition-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-30T13:04:50+00:00</t>
+    <t>2025-01-31T16:23:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/examples/ValueSet-condition-valueset.xlsx
+++ b/branches/examples/ValueSet-condition-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-31T16:23:22+00:00</t>
+    <t>2025-02-03T12:16:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/examples/ValueSet-condition-valueset.xlsx
+++ b/branches/examples/ValueSet-condition-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-03T12:16:06+00:00</t>
+    <t>2025-02-17T11:11:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/examples/ValueSet-condition-valueset.xlsx
+++ b/branches/examples/ValueSet-condition-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-17T11:11:18+00:00</t>
+    <t>2025-02-17T11:15:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/examples/ValueSet-condition-valueset.xlsx
+++ b/branches/examples/ValueSet-condition-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-17T11:15:32+00:00</t>
+    <t>2025-02-19T10:40:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
